--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
@@ -39,21 +39,21 @@
     <t xml:space="preserve">Alto Hospicio</t>
   </si>
   <si>
+    <t xml:space="preserve">Colchane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiña</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pica</t>
   </si>
   <si>
-    <t xml:space="preserve">Colchane</t>
+    <t xml:space="preserve">Huara</t>
   </si>
   <si>
     <t xml:space="preserve">Pozo Almonte</t>
   </si>
   <si>
-    <t xml:space="preserve">Camiña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huara</t>
-  </si>
-  <si>
     <t xml:space="preserve">Iquique</t>
   </si>
   <si>
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -496,7 +496,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3871</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="3">
@@ -507,13 +507,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>385</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -524,13 +524,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>351</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -541,13 +541,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>321</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="6">
@@ -558,13 +558,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>50</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="7">
@@ -575,13 +575,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-12</v>
+        <v>-240</v>
       </c>
     </row>
     <row r="8">
@@ -598,7 +598,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-12077</v>
+        <v>-3802</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:16</t>
+    <t xml:space="preserve">2026-10-05 08:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
